--- a/panchang-data/Vidisha2026.xlsx
+++ b/panchang-data/Vidisha2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5399">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16222,6 +16222,9 @@
   </si>
   <si>
     <t>121°05'04.82</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16711,7 +16714,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16797,7 +16800,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16883,7 +16886,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16969,7 +16972,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17055,7 +17058,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17141,7 +17144,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17227,7 +17230,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17313,7 +17316,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17399,7 +17402,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17485,7 +17488,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17571,7 +17574,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17657,7 +17660,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17743,7 +17746,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17829,7 +17832,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17915,7 +17918,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18001,7 +18004,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18087,7 +18090,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18173,7 +18176,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18259,7 +18262,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18345,7 +18348,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18431,7 +18434,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18517,7 +18520,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18603,7 +18606,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18689,7 +18692,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18775,7 +18778,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18861,7 +18864,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18947,7 +18950,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19033,7 +19036,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19119,7 +19122,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19205,7 +19208,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19291,7 +19294,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19377,7 +19380,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>568</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19463,7 +19466,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19549,7 +19552,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19635,7 +19638,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19721,7 +19724,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19807,7 +19810,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19893,7 +19896,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19979,7 +19982,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20065,7 +20068,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20151,7 +20154,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20237,7 +20240,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20323,7 +20326,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20409,7 +20412,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20495,7 +20498,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20581,7 +20584,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20667,7 +20670,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20753,7 +20756,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20839,7 +20842,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20925,7 +20928,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21011,7 +21014,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21097,7 +21100,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21183,7 +21186,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21269,7 +21272,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21355,7 +21358,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21441,7 +21444,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21527,7 +21530,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21613,7 +21616,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21699,7 +21702,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21785,7 +21788,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21871,7 +21874,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21957,7 +21960,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>568</v>
+        <v>1010</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22043,7 +22046,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22129,7 +22132,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22215,7 +22218,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22301,7 +22304,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22387,7 +22390,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22473,7 +22476,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22559,7 +22562,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22645,7 +22648,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22731,7 +22734,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22817,7 +22820,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22903,7 +22906,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -22989,7 +22992,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23075,7 +23078,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23161,7 +23164,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23247,7 +23250,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23333,7 +23336,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23419,7 +23422,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23505,7 +23508,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23591,7 +23594,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23677,7 +23680,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23763,7 +23766,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23849,7 +23852,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23935,7 +23938,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24021,7 +24024,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24107,7 +24110,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24193,7 +24196,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24279,7 +24282,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24365,7 +24368,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24451,7 +24454,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24537,7 +24540,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1010</v>
+        <v>1450</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24623,7 +24626,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24709,7 +24712,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24795,7 +24798,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24881,7 +24884,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24967,7 +24970,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25053,7 +25056,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25139,7 +25142,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25225,7 +25228,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25311,7 +25314,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25397,7 +25400,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25483,7 +25486,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25569,7 +25572,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25655,7 +25658,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25741,7 +25744,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25827,7 +25830,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25913,7 +25916,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -25999,7 +26002,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26085,7 +26088,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26171,7 +26174,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26257,7 +26260,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26343,7 +26346,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26429,7 +26432,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26515,7 +26518,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26601,7 +26604,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26687,7 +26690,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26773,7 +26776,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26859,7 +26862,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26945,7 +26948,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27031,7 +27034,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1450</v>
+        <v>1874</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27117,7 +27120,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27203,7 +27206,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27289,7 +27292,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27375,7 +27378,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27461,7 +27464,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27547,7 +27550,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27633,7 +27636,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27719,7 +27722,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27805,7 +27808,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27891,7 +27894,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27977,7 +27980,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28063,7 +28066,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28149,7 +28152,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28235,7 +28238,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28321,7 +28324,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1874</v>
+        <v>2310</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28407,7 +28410,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28493,7 +28496,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28579,7 +28582,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28665,7 +28668,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28751,7 +28754,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28837,7 +28840,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28923,7 +28926,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29009,7 +29012,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29095,7 +29098,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29181,7 +29184,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29267,7 +29270,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29353,7 +29356,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29439,7 +29442,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29525,7 +29528,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29611,7 +29614,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1874</v>
+        <v>5398</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29697,7 +29700,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29783,7 +29786,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29869,7 +29872,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29955,7 +29958,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30041,7 +30044,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30127,7 +30130,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30213,7 +30216,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30299,7 +30302,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30385,7 +30388,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30471,7 +30474,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30557,7 +30560,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30643,7 +30646,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30729,7 +30732,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30815,7 +30818,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30901,7 +30904,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2310</v>
+        <v>5398</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
